--- a/out/european-energy-software-2026.xlsx
+++ b/out/european-energy-software-2026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rensource Energy</t>
+          <t>Ostrom</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>https://rensource.energy/</t>
+          <t>https://ostrom.de/</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Ostrom</t>
+          <t>Tibber</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>https://ostrom.de/</t>
+          <t>https://tibber.com/</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Tibber</t>
+          <t>Octopus Energy</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>https://tibber.com/</t>
+          <t>https://octopus.energy/</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Octopus Energy</t>
+          <t>Voltiq</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>https://octopus.energy/</t>
+          <t>https://voltiq.de/</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Voltiq</t>
+          <t>Yuso</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>https://voltiq.de/</t>
+          <t>https://yuso.energy/</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Yuso</t>
+          <t>Enervalis</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>https://yuso.energy/</t>
+          <t>https://enervalis.com/</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Enervalis</t>
+          <t>Flexidao</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>https://enervalis.com/</t>
+          <t>https://flexidao.com/</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Flexidao</t>
+          <t>Greenely</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>https://flexidao.com/</t>
+          <t>https://greenely.se/</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Greenely</t>
+          <t>Barbara IoT</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>https://greenely.se/</t>
+          <t>https://barbara.tech/</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Barbara IoT</t>
+          <t>Entrnce</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -1067,12 +1067,1307 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>https://entrnce.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Plentify</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>https://plentify.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Powerdale</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>https://powerdale.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Kiwi Power</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>https://kiwipowered.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Limejump</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>https://limejump.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Piclo</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>https://piclo.energy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Enphase Europe</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="3" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>https://enphase.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Sonnen</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="3" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>https://sonnen.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Greenbyte</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="3" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>https://greenbyte.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Enevo</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>https://enevo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Smartvatten</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>https://smartvatten.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Ngrid / National Grid ESO</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>https://nationalgrideso.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Bulb Energy</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>https://bulb.co.uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Lichtblick</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="3" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>https://lichtblick.de/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Rabot Charge</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
+      <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>https://rabot.charge/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Energi Danmark</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="3" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>https://energidanmark.dk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Cenergy</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="3" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>https://cenergy.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Wondr Energy</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>https://wondrenergy.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Otovo</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>https://otovo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Svea Solar</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n"/>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="n"/>
+      <c r="L35" s="3" t="n"/>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>https://sveasolar.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Oda Networks</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n"/>
+      <c r="E36" s="3" t="n"/>
+      <c r="F36" s="3" t="n"/>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
+      <c r="M36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>https://odanetworks.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Centrica Business Solutions</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n"/>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="3" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
+      <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>https://centrica.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Engie Impact</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n"/>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
+      <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>https://engieimpact.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Next Kraftwerke</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>https://next-kraftwerke.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Statkraft Markets</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
+      <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>https://statkraft.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Axpo</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n"/>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="n"/>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>https://axpo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Danske Commodities</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="n"/>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>https://danskecommodities.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Repsol Digital Energy</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>https://barbara.tech/</t>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>https://repsol.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Enapter</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
+      <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>https://enapter.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Predictix Energy</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
+      <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>https://predictix.io/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>E-Chargers</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="M46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>https://e-chargers.fr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Smappee</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n"/>
+      <c r="E47" s="3" t="n"/>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
+      <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>https://smappee.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Voltaware</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n"/>
+      <c r="E48" s="3" t="n"/>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
+      <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>https://voltaware.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Switchee</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n"/>
+      <c r="E49" s="3" t="n"/>
+      <c r="F49" s="3" t="n"/>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
+      <c r="M49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>https://switchee.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Loop Energy Saver</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n"/>
+      <c r="E50" s="3" t="n"/>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
+      <c r="M50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>https://loop.homes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Zuper</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n"/>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
+      <c r="M51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>https://zuper.de/</t>
         </is>
       </c>
     </row>
